--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -526,6 +526,9 @@
       <c r="A11" t="str">
         <v>5</v>
       </c>
+      <c r="C11" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -529,10 +529,96 @@
       <c r="C11" t="str">
         <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>455_粉星花_tweedia pink_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>6</v>
+      </c>
+      <c r="C15" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>528_五代果_pig face_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>229_黄蝴蝶_Yellow Butterfly_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>7</v>
+      </c>
+      <c r="C20" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,7 +673,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0194120205080120806800</v>
+        <v>0194120205080120806808211861215151510120</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -615,6 +615,9 @@
       <c r="C21" t="str">
         <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>1=5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -673,7 +676,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0194120205080120806808211861215151510120</v>
+        <v>0194120205080120806808211861215151510121=5</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -616,7 +616,7 @@
         <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F21" t="str">
-        <v>1=5</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -676,7 +676,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0194120205080120806808211861215151510121=5</v>
+        <v>01941202050801208068082118612151515101215</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -616,12 +616,92 @@
         <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F21" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>528_五代果_pig face_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
         <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>8</v>
+      </c>
+      <c r="C26" t="str">
+        <v>8_冰淇淋洋桔梗_Icecream Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F26" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>259_诺拉_Nora_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>528_五代果_pig face_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>276_情迷罗拉_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -676,7 +756,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01941202050801208068082118612151515101215</v>
+        <v>019412020508012080680821186121515151012522020152211183140</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -698,6 +698,9 @@
       <c r="C31" t="str">
         <v>276_情迷罗拉_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -756,7 +759,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>019412020508012080680821186121515151012522020152211183140</v>
+        <v>019412020508012080680821186121515151012522020152211183145</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -702,9 +702,92 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>579_腊梅红_wax red_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>9</v>
+      </c>
+      <c r="C33" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>8_冰淇淋洋桔梗_Icecream Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F34" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>10</v>
+      </c>
+      <c r="C36" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>276_情迷罗拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>577_腊梅白_wax white_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>578_腊梅粉_wax pink_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -759,7 +842,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>019412020508012080680821186121515151012522020152211183145</v>
+        <v>0194120205080120806808211861215151510125220201522111831452030202512123020200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -784,6 +784,9 @@
       <c r="A41" t="str">
         <v>11</v>
       </c>
+      <c r="C41" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -787,6 +787,9 @@
       <c r="C41" t="str">
         <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -845,7 +848,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0194120205080120806808211861215151510125220201522111831452030202512123020200</v>
+        <v>01941202050801208068082118612151515101252202015221118314520302025121230202012</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -791,9 +791,101 @@
         <v>12</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>259_诺拉_Nora_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>12</v>
+      </c>
+      <c r="C46" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>13</v>
+      </c>
+      <c r="C47" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>14</v>
+      </c>
+      <c r="C48" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>15</v>
+      </c>
+      <c r="C49" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>16</v>
+      </c>
+      <c r="C50" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -848,7 +940,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01941202050801208068082118612151515101252202015221118314520302025121230202012</v>
+        <v>01941202050801208068082118612151515101252202015221118314520302025121230202012201094540404040100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -882,6 +882,9 @@
       <c r="C51" t="str">
         <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F51" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -940,7 +943,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01941202050801208068082118612151515101252202015221118314520302025121230202012201094540404040100</v>
+        <v>01941202050801208068082118612151515101252202015221118314520302025121230202012201094540404040101</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -886,9 +886,89 @@
         <v>1</v>
       </c>
     </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>528_五代果_pig face_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>8_冰淇淋洋桔梗_Icecream Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F55" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>17</v>
+      </c>
+      <c r="C57" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>528_五代果_pig face_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>506_紫罗兰香槟色_violet champagne_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -943,7 +1023,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01941202050801208068082118612151515101252202015221118314520302025121230202012201094540404040101</v>
+        <v>0194120205080120806808211861215151510125220201522111831452030202512123020201220109454040404010119138860154020200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -965,6 +965,9 @@
       <c r="C61" t="str">
         <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
       </c>
+      <c r="F61" t="str">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1023,7 +1026,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0194120205080120806808211861215151510125220201522111831452030202512123020201220109454040404010119138860154020200</v>
+        <v>019412020508012080680821186121515151012522020152211183145203020251212302020122010945404040401011913886015402020100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -969,9 +969,95 @@
         <v>100</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>18</v>
+      </c>
+      <c r="C62" t="str">
+        <v>406_千鸟飞燕 白_larkspur white_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>500_千鸟飞燕 粉_larkspur pink_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>492_细米花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>19</v>
+      </c>
+      <c r="C65" t="str">
+        <v>492_细米花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>514_松虫草紫_scabiosa purple_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>20</v>
+      </c>
+      <c r="C68" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F68" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F69" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>421_松虫草黑色_scabiosa black_undefined_1bunch</v>
+      </c>
+      <c r="F70" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1026,7 +1112,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>019412020508012080680821186121515151012522020152211183145203020251212302020122010945404040401011913886015402020100</v>
+        <v>0194120205080120806808211861215151510125220201522111831452030202512123020201220109454040404010119138860154020201003031104020202022200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -1054,6 +1054,9 @@
       <c r="C71" t="str">
         <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
       </c>
+      <c r="F71" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1112,7 +1115,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0194120205080120806808211861215151510125220201522111831452030202512123020201220109454040404010119138860154020201003031104020202022200</v>
+        <v>01941202050801208068082118612151515101252202015221118314520302025121230202012201094540404040101191388601540202010030311040202020222020</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L80"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1058,9 +1058,93 @@
         <v>20</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>21</v>
+      </c>
+      <c r="C72" t="str">
+        <v>394_矢车菊_Cornflower_undefined_1bunch</v>
+      </c>
+      <c r="F72" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>394_矢车菊_Cornflower_undefined_1bunch</v>
+      </c>
+      <c r="F73" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="str">
+        <v>394_矢车菊_Cornflower_undefined_1bunch</v>
+      </c>
+      <c r="F74" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" xml:space="preserve">
+      <c r="C75" t="str" xml:space="preserve">
+        <v xml:space="preserve">405_小飞燕浅蓝_ delphinium ballkleid
+dark blue_undefined_1bunch</v>
+      </c>
+      <c r="F75" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" xml:space="preserve">
+      <c r="C76" t="str" xml:space="preserve">
+        <v xml:space="preserve">499_小飞燕浅蓝_delphinium ballkleid
+light blue_undefined_1bunch</v>
+      </c>
+      <c r="F76" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>22</v>
+      </c>
+      <c r="C77" t="str">
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
+      </c>
+      <c r="F77" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F78" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" xml:space="preserve">
+      <c r="C79" t="str" xml:space="preserve">
+        <v xml:space="preserve">404_小飞燕白色_ delphinium ballkleid
+white_undefined_1bunch</v>
+      </c>
+      <c r="F79" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>23</v>
+      </c>
+      <c r="C80" t="str">
+        <v>629_干花蓬莱松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F80" t="str">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L80"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1115,7 +1199,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01941202050801208068082118612151515101252202015221118314520302025121230202012201094540404040101191388601540202010030311040202020222020</v>
+        <v>0194120205080120806808211861215151510125220201522111831452030202512123020201220109454040404010119138860154020201003031104020202022202028303151520202020</v>
       </c>
     </row>
   </sheetData>
